--- a/sample_data/E_monthly_uploads/2026-08_maadi_report.xlsx
+++ b/sample_data/E_monthly_uploads/2026-08_maadi_report.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,11 @@
           <t>تاريخ الصلاحية</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>الشركة</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -522,6 +527,11 @@
       <c r="J5" s="1" t="n">
         <v>46807</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -560,6 +570,11 @@
       <c r="J6" s="1" t="n">
         <v>46941</v>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -598,6 +613,11 @@
       <c r="J7" s="1" t="n">
         <v>46673</v>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -638,6 +658,11 @@
           <t>06/2028</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -678,6 +703,11 @@
           <t>28-01-2028</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -718,6 +748,11 @@
       <c r="J10" s="1" t="n">
         <v>46600</v>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -758,6 +793,11 @@
       <c r="J11" s="1" t="n">
         <v>46947</v>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -798,6 +838,11 @@
           <t>01/2027</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -838,6 +883,11 @@
       <c r="J13" s="1" t="n">
         <v>46848</v>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -878,6 +928,11 @@
           <t>15-06-2028</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -916,6 +971,11 @@
       <c r="J15" s="1" t="n">
         <v>46387</v>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -958,6 +1018,11 @@
           <t>06/2028</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -996,6 +1061,11 @@
       <c r="J17" s="1" t="n">
         <v>46802</v>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1036,6 +1106,11 @@
       <c r="J18" s="1" t="n">
         <v>46619</v>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1076,6 +1151,11 @@
           <t>04-08-2027</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1116,6 +1196,11 @@
           <t>01/2027</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1154,6 +1239,11 @@
       <c r="J21" s="1" t="n">
         <v>47064</v>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1196,6 +1286,11 @@
       <c r="J22" s="1" t="n">
         <v>46340</v>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1231,6 +1326,11 @@
       <c r="I23" t="n">
         <v>11.22</v>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1271,6 +1371,11 @@
           <t>01/2028</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1311,6 +1416,11 @@
       <c r="J25" s="1" t="n">
         <v>46657</v>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1349,6 +1459,11 @@
       <c r="J26" s="1" t="n">
         <v>46978</v>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1387,6 +1502,11 @@
       <c r="J27" s="1" t="n">
         <v>47207</v>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1429,6 +1549,11 @@
           <t>10/2027</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1464,6 +1589,11 @@
       <c r="I29" t="n">
         <v>327.93</v>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1502,6 +1632,11 @@
       <c r="J30" s="1" t="n">
         <v>46776</v>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1542,6 +1677,11 @@
       <c r="J31" s="1" t="n">
         <v>47079</v>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1584,6 +1724,11 @@
           <t>12/2026</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1622,6 +1767,11 @@
       <c r="J33" s="1" t="n">
         <v>46337</v>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1664,6 +1814,11 @@
           <t>04-12-2027</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1702,6 +1857,11 @@
       <c r="J35" s="1" t="n">
         <v>47019</v>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1742,6 +1902,11 @@
           <t>01/2027</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1780,6 +1945,11 @@
       <c r="J37" s="1" t="n">
         <v>46857</v>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1818,6 +1988,11 @@
       <c r="J38" s="1" t="n">
         <v>47187</v>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1860,6 +2035,11 @@
           <t>25-03-2028</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1904,6 +2084,11 @@
           <t>03/2028</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1942,6 +2127,11 @@
       <c r="J41" s="1" t="n">
         <v>46632</v>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1980,6 +2170,11 @@
       <c r="J42" s="1" t="n">
         <v>46649</v>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>GSK Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2018,6 +2213,11 @@
       <c r="J43" s="1" t="n">
         <v>46893</v>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2058,6 +2258,11 @@
           <t>05/2027</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2108,6 +2313,11 @@
       <c r="J46" t="inlineStr">
         <is>
           <t>تاريخ الصلاحية</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>الشركة</t>
         </is>
       </c>
     </row>
@@ -2148,6 +2358,11 @@
       <c r="J47" s="1" t="n">
         <v>46989</v>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2190,6 +2405,11 @@
       <c r="J48" s="1" t="n">
         <v>46958</v>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2228,6 +2448,11 @@
       <c r="J49" s="1" t="n">
         <v>46566</v>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2268,6 +2493,11 @@
           <t>01/2029</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2310,6 +2540,11 @@
           <t>22-02-2028</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2348,6 +2583,11 @@
       <c r="J52" s="1" t="n">
         <v>47149</v>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2386,6 +2626,11 @@
       <c r="J53" s="1" t="n">
         <v>46384</v>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2428,6 +2673,11 @@
           <t>02/2029</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2468,6 +2718,11 @@
       <c r="J55" s="1" t="n">
         <v>46317</v>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2503,6 +2758,11 @@
       <c r="I56" t="n">
         <v>153.87</v>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2541,6 +2801,11 @@
       <c r="J57" s="1" t="n">
         <v>46794</v>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2581,6 +2846,11 @@
           <t>08/2028</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2619,6 +2889,11 @@
       <c r="J59" s="1" t="n">
         <v>46739</v>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2661,6 +2936,11 @@
       <c r="J60" s="1" t="n">
         <v>47057</v>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2701,6 +2981,11 @@
           <t>12-06-2028</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2738,6 +3023,11 @@
       <c r="I62" t="n">
         <v>775.2</v>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2776,6 +3066,11 @@
       <c r="J63" s="1" t="n">
         <v>46973</v>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2814,6 +3109,11 @@
       <c r="J64" s="1" t="n">
         <v>46849</v>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2852,6 +3152,11 @@
       <c r="J65" s="1" t="n">
         <v>46828</v>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Beauty Hub</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2894,6 +3199,11 @@
           <t>04/2028</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2932,6 +3242,11 @@
       <c r="J67" s="1" t="n">
         <v>46802</v>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>United Company</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2970,6 +3285,11 @@
       <c r="J68" s="1" t="n">
         <v>47048</v>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3012,6 +3332,11 @@
       <c r="J69" s="1" t="n">
         <v>47012</v>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3052,6 +3377,11 @@
           <t>07/2028</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3092,6 +3422,11 @@
           <t>15-05-2028</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Mother &amp; Baby Co</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3132,6 +3467,11 @@
       <c r="J72" s="1" t="n">
         <v>47157</v>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3170,6 +3510,11 @@
       <c r="J73" s="1" t="n">
         <v>47123</v>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3210,6 +3555,11 @@
           <t>08/2028</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3248,6 +3598,11 @@
       <c r="J75" s="1" t="n">
         <v>47011</v>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3290,6 +3645,11 @@
           <t>24-02-2028</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3328,6 +3688,11 @@
       <c r="J77" s="1" t="n">
         <v>46997</v>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3372,6 +3737,11 @@
           <t>11/2028</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3410,6 +3780,11 @@
       <c r="J79" s="1" t="n">
         <v>46980</v>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Pharma Overseas</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3448,6 +3823,11 @@
       <c r="J80" s="1" t="n">
         <v>47126</v>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3488,6 +3868,11 @@
           <t>17-10-2027</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3528,6 +3913,11 @@
           <t>01/2028</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Ibnsina Pharma</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3565,6 +3955,11 @@
       <c r="I83" t="n">
         <v>418.38</v>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3605,6 +4000,11 @@
       <c r="J84" s="1" t="n">
         <v>46401</v>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3643,6 +4043,11 @@
       <c r="J85" s="1" t="n">
         <v>46320</v>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3681,6 +4086,11 @@
       <c r="J86" t="inlineStr">
         <is>
           <t>08/2028</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>MedTech Supplies</t>
         </is>
       </c>
     </row>
